--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260806.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>202608WTEQ6F</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>104,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>202608WTEQ6F</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>104,000</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>46,000</t>
+          <t>4,620,578</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>4,620,578</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>97,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>97,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>5,145,956</t>
+          <t>805,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>805,000</t>
+          <t>5,145,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>404,000</t>
+          <t>236,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>301,000</t>
+          <t>1,618,400</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>236,000</t>
+          <t>301,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,618,400</t>
+          <t>404,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,040,121</t>
+          <t>1,823,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,823,000</t>
+          <t>1,040,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>185,000</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>264,000</t>
+          <t>705,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>264,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>705,000</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
